--- a/수련지도_입력양식_산부인과.xlsx
+++ b/수련지도_입력양식_산부인과.xlsx
@@ -671,7 +671,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" s="21">
+    <row r="2" ht="74" customHeight="1" s="21">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>’26.7월</t>
@@ -687,7 +687,9 @@
       </c>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>총 7건
+· 현장 교육 3건: 산과 외래 참관 교육
+· 이론 교육 4건: 부인암의 기초, 무월경·PCOS·자궁내막증, 태아 선천성 심장질환(역학·해부)</t>
         </is>
       </c>
     </row>
@@ -755,7 +757,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1" s="21">
+    <row r="7" ht="57" customHeight="1" s="21">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>’26.8월</t>
@@ -771,7 +773,9 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>총 6건
+· 현장 교육 4건: 산과 외래 참관 교육, 외래 초음파
+· 이론 교육 2건: 조기난소부전·사산·태아 심장 해부, 태아심장 복습·유산 북리딩</t>
         </is>
       </c>
     </row>
@@ -803,7 +807,7 @@
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>총 1건: 신규 1년차용 인계 확인</t>
         </is>
       </c>
     </row>
@@ -977,7 +981,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="76" customHeight="1" s="21">
+    <row r="2" ht="133" customHeight="1" s="21">
       <c r="A2" s="11" t="inlineStr">
         <is>
           <t>책임 지도전문의</t>
@@ -1000,10 +1004,13 @@
       </c>
       <c r="E2" s="26" t="inlineStr">
         <is>
-          <t>9월 수련지도 : 20건 (현장 교육 18, 이론 교육 2)
+          <t>7월 수련지도 : 4건 (이론 교육 4)
+8월 수련지도 : 3건 (현장 교육 1, 이론 교육 2)
+8월 간담회 : 1건
+9월 수련지도 : 20건 (현장 교육 18, 이론 교육 2)
 9월 간담회 : 2건
 9월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 2, 진로·진학 1)
-합계 : 25건</t>
+합계 : 33건</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1044,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="38" customHeight="1" s="21">
+    <row r="4" ht="76" customHeight="1" s="21">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1060,8 +1067,10 @@
       </c>
       <c r="E4" s="27" t="inlineStr">
         <is>
-          <t>9월 수련지도 : 4건 (현장 교육 4)
-합계 : 4건</t>
+          <t>7월 수련지도 : 3건 (현장 교육 3)
+8월 수련지도 : 3건 (현장 교육 3)
+9월 수련지도 : 4건 (현장 교육 4)
+합계 : 10건</t>
         </is>
       </c>
     </row>

--- a/수련지도_입력양식_산부인과.xlsx
+++ b/수련지도_입력양식_산부인과.xlsx
@@ -182,7 +182,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -264,6 +264,14 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -694,7 +702,7 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" s="21">
-      <c r="A3" s="23" t="n"/>
+      <c r="A3" s="28" t="n"/>
       <c r="B3" s="7" t="n">
         <v>2</v>
       </c>
@@ -710,7 +718,7 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" s="21">
-      <c r="A4" s="23" t="n"/>
+      <c r="A4" s="28" t="n"/>
       <c r="B4" s="7" t="n">
         <v>3</v>
       </c>
@@ -726,7 +734,7 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" s="21">
-      <c r="A5" s="23" t="n"/>
+      <c r="A5" s="28" t="n"/>
       <c r="B5" s="7" t="n">
         <v>4</v>
       </c>
@@ -742,7 +750,7 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" s="21">
-      <c r="A6" s="24" t="n"/>
+      <c r="A6" s="29" t="n"/>
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
@@ -780,7 +788,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="21">
-      <c r="A8" s="23" t="n"/>
+      <c r="A8" s="28" t="n"/>
       <c r="B8" s="7" t="n">
         <v>2</v>
       </c>
@@ -796,7 +804,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="21">
-      <c r="A9" s="23" t="n"/>
+      <c r="A9" s="28" t="n"/>
       <c r="B9" s="7" t="n">
         <v>3</v>
       </c>
@@ -812,7 +820,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="21">
-      <c r="A10" s="23" t="n"/>
+      <c r="A10" s="28" t="n"/>
       <c r="B10" s="7" t="n">
         <v>4</v>
       </c>
@@ -828,7 +836,7 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" s="21">
-      <c r="A11" s="24" t="n"/>
+      <c r="A11" s="29" t="n"/>
       <c r="B11" s="1" t="n">
         <v>5</v>
       </c>
@@ -866,7 +874,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="21">
-      <c r="A13" s="23" t="n"/>
+      <c r="A13" s="28" t="n"/>
       <c r="B13" s="7" t="n">
         <v>2</v>
       </c>
@@ -882,7 +890,7 @@
       </c>
     </row>
     <row r="14" ht="40" customHeight="1" s="21">
-      <c r="A14" s="23" t="n"/>
+      <c r="A14" s="28" t="n"/>
       <c r="B14" s="7" t="n">
         <v>3</v>
       </c>
@@ -898,7 +906,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="21">
-      <c r="A15" s="23" t="n"/>
+      <c r="A15" s="28" t="n"/>
       <c r="B15" s="7" t="n">
         <v>4</v>
       </c>
@@ -914,7 +922,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="21">
-      <c r="A16" s="24" t="n"/>
+      <c r="A16" s="29" t="n"/>
       <c r="B16" s="1" t="n">
         <v>5</v>
       </c>
@@ -951,7 +959,7 @@
     <col width="27.125" customWidth="1" style="21" min="1" max="1"/>
     <col width="30" customWidth="1" style="21" min="3" max="3"/>
     <col width="20.75" customWidth="1" style="21" min="4" max="4"/>
-    <col width="80" customWidth="1" style="21" min="5" max="5"/>
+    <col width="85" customWidth="1" style="21" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="21">
@@ -981,7 +989,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="133" customHeight="1" s="21">
+    <row r="2" ht="108" customHeight="1" s="21">
       <c r="A2" s="11" t="inlineStr">
         <is>
           <t>책임 지도전문의</t>
@@ -1002,19 +1010,18 @@
           <t>26.07.01~</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
-        <is>
-          <t>7월 수련지도 : 4건 (이론 교육 4)
-8월 수련지도 : 3건 (현장 교육 1, 이론 교육 2)
-8월 간담회 : 1건
-9월 수련지도 : 20건 (현장 교육 18, 이론 교육 2)
-9월 간담회 : 2건
-9월 개별 면담 : 3건 (분야별: 수련·근무 3, 학습·역량 2, 진로·진학 1)
-합계 : 33건</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="76" customHeight="1" s="21">
+      <c r="E2" s="30" t="inlineStr">
+        <is>
+          <t>7월 수련지도 : 부인암·생식내분비·태아심장 강의(김채연, 박민영, 이지수)
+8월 간담회 : 신규 1년차용 인계 확인(박민영, 이지수)
+8월 수련지도 : 태아심장·조기난소부전 강의, 외래 초음파(김채연, 박민영, 이지수)
+9월 간담회 : 1년차 교육 점검, 제왕절개 순서·추석 당직 대비(신민석, 김채연, 박민영, 이지수)
+9월 면담 : 수련 환경·1년차 고충 상담(김소윤, 신민석, 박민영)
+9월 수련지도 : 외래 초음파, 수술실(제왕절개·복강경), 분만실·병동·응급실 현장 지도(김소윤, 신민석, 김채연, 박민영, 이지수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="57" customHeight="1" s="21">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1035,16 +1042,15 @@
           <t>26.07.01~</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
-        <is>
-          <t>9월 수련지도 : 1건 (이론 교육 1)
-9월 학술집담회 : 3건
-9월 개별 면담 : 1건 (분야별: 수련·근무 1, 진로·진학 1)
-합계 : 5건</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="76" customHeight="1" s="21">
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>9월 학술집담회 : 튜머보드, 저널리뷰(김소윤, 신민석, 김채연, 박민영, 이지수)
+9월 면담 : 수련 및 진로 상담(김소윤, 신민석)
+9월 수련지도 : 자궁경부암 치료 가이드라인 강의(김소윤, 신민석, 김채연, 박민영, 이지수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="57" customHeight="1" s="21">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1065,12 +1071,11 @@
           <t>26.07.01~</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
-        <is>
-          <t>7월 수련지도 : 3건 (현장 교육 3)
-8월 수련지도 : 3건 (현장 교육 3)
-9월 수련지도 : 4건 (현장 교육 4)
-합계 : 10건</t>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>7월 수련지도 : 산과 외래 참관 교육(김채연, 박민영, 이지수)
+8월 수련지도 : 산과 외래 참관 교육(김채연, 박민영, 이지수)
+9월 수련지도 : 산과 외래 참관 교육(김소윤, 신민석, 김채연, 박민영, 이지수)</t>
         </is>
       </c>
     </row>

--- a/수련지도_입력양식_산부인과.xlsx
+++ b/수련지도_입력양식_산부인과.xlsx
@@ -10,14 +10,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -71,6 +71,15 @@
       <sz val="13"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -153,18 +162,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -182,37 +185,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -222,40 +210,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -264,6 +225,30 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -273,6 +258,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -653,47 +642,47 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="23.125" customWidth="1" style="21" min="3" max="3"/>
-    <col width="70" customWidth="1" style="21" min="4" max="4"/>
+    <col width="23.125" customWidth="1" style="9" min="3" max="3"/>
+    <col width="70" customWidth="1" style="9" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51.75" customHeight="1" s="21">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="51.75" customHeight="1" s="9">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>연번</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>월별 중점 지도 내용</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="74" customHeight="1" s="21">
-      <c r="A2" s="1" t="inlineStr">
+    <row r="2" ht="74.09999999999999" customHeight="1" s="9">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>’26.7월</t>
         </is>
       </c>
-      <c r="B2" s="7" t="n">
+      <c r="B2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>수련지도</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>총 7건
 · 현장 교육 3건: 산과 외래 참관 교육
@@ -701,85 +690,85 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" s="21">
-      <c r="A3" s="28" t="n"/>
-      <c r="B3" s="7" t="n">
+    <row r="3" ht="24" customHeight="1" s="9">
+      <c r="A3" s="22" t="n"/>
+      <c r="B3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>학술집담회</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" s="21">
-      <c r="A4" s="28" t="n"/>
-      <c r="B4" s="7" t="n">
+    <row r="4" ht="24" customHeight="1" s="9">
+      <c r="A4" s="22" t="n"/>
+      <c r="B4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>간담회</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1" s="21">
-      <c r="A5" s="28" t="n"/>
-      <c r="B5" s="7" t="n">
+    <row r="5" ht="24" customHeight="1" s="9">
+      <c r="A5" s="22" t="n"/>
+      <c r="B5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>개별 면담</t>
         </is>
       </c>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" s="21">
-      <c r="A6" s="29" t="n"/>
-      <c r="B6" s="1" t="n">
+    <row r="6" ht="24" customHeight="1" s="9">
+      <c r="A6" s="23" t="n"/>
+      <c r="B6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="57" customHeight="1" s="21">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="7" ht="57" customHeight="1" s="9">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>’26.8월</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>수련지도</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>총 6건
 · 현장 교육 4건: 산과 외래 참관 교육, 외래 초음파
@@ -787,85 +776,85 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1" s="21">
-      <c r="A8" s="28" t="n"/>
-      <c r="B8" s="7" t="n">
+    <row r="8" ht="24" customHeight="1" s="9">
+      <c r="A8" s="22" t="n"/>
+      <c r="B8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>학술집담회</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" s="21">
-      <c r="A9" s="28" t="n"/>
-      <c r="B9" s="7" t="n">
+    <row r="9" ht="24" customHeight="1" s="9">
+      <c r="A9" s="22" t="n"/>
+      <c r="B9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>간담회</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>총 1건: 신규 1년차용 인계 확인</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" s="21">
-      <c r="A10" s="28" t="n"/>
-      <c r="B10" s="7" t="n">
+    <row r="10" ht="24" customHeight="1" s="9">
+      <c r="A10" s="22" t="n"/>
+      <c r="B10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>개별 면담</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" s="21">
-      <c r="A11" s="29" t="n"/>
-      <c r="B11" s="1" t="n">
+    <row r="11" ht="24" customHeight="1" s="9">
+      <c r="A11" s="23" t="n"/>
+      <c r="B11" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="91" customHeight="1" s="21">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="12" ht="90.95" customHeight="1" s="9">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>’26.9월</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>수련지도</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>총 25건
 · 현장 교육 22건: 외래 초음파·산과 외래 참관, 수술실(제왕절개·복강경·자궁경·LaRSO), 분만실·병동(자연·유도분만, 회진), 응급실(초기 산모)
@@ -873,65 +862,65 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1" s="21">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="7" t="n">
+    <row r="13" ht="24" customHeight="1" s="9">
+      <c r="A13" s="22" t="n"/>
+      <c r="B13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>학술집담회</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>총 3건: 튜머보드 1, 저널리뷰 2</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1" s="21">
-      <c r="A14" s="28" t="n"/>
-      <c r="B14" s="7" t="n">
+    <row r="14" ht="39.95" customHeight="1" s="9">
+      <c r="A14" s="22" t="n"/>
+      <c r="B14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>간담회</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>총 2건: 1년차 마지막 주 간담회(신입 1년차 교육 점검·과 운영 방안), 제왕절개 순서·추석 당직 대비</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" s="21">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="7" t="n">
+    <row r="15" ht="24" customHeight="1" s="9">
+      <c r="A15" s="22" t="n"/>
+      <c r="B15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>개별 면담</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>총 4건 (분야: 수련·근무 4, 학습·역량 2, 진로·진학 2)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1" s="21">
-      <c r="A16" s="29" t="n"/>
-      <c r="B16" s="1" t="n">
+    <row r="16" ht="24" customHeight="1" s="9">
+      <c r="A16" s="23" t="n"/>
+      <c r="B16" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>해당 없음</t>
         </is>
@@ -953,64 +942,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="27.125" customWidth="1" style="21" min="1" max="1"/>
-    <col width="30" customWidth="1" style="21" min="3" max="3"/>
-    <col width="20.75" customWidth="1" style="21" min="4" max="4"/>
-    <col width="85" customWidth="1" style="21" min="5" max="5"/>
+    <col width="27.125" customWidth="1" style="9" min="1" max="1"/>
+    <col width="30" customWidth="1" style="9" min="3" max="3"/>
+    <col width="20.75" customWidth="1" style="9" min="4" max="4"/>
+    <col width="85" customWidth="1" style="9" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1" s="21">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="9">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>지도 전문의 유형</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>성명</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>지도대상 전공의</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>사업 참여기간</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>수련 세부 내용</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="108" customHeight="1" s="21">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="108" customHeight="1" s="9">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>책임 지도전문의</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>금지현</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>김소윤, 신민석(1년차), 김채연, 박민영, 이지수(2년차)</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>김소윤, 신민석, 김채연, 박민영, 이지수</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>26.07.01~</t>
         </is>
       </c>
-      <c r="E2" s="30" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>7월 수련지도 : 부인암·생식내분비·태아심장 강의(김채연, 박민영, 이지수)
 8월 간담회 : 신규 1년차용 인계 확인(박민영, 이지수)
@@ -1021,28 +1010,28 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="57" customHeight="1" s="21">
-      <c r="A3" s="11" t="inlineStr">
+    <row r="3" ht="57" customHeight="1" s="9">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>교육전담</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>배재만</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
-        <is>
-          <t>김소윤, 신민석(1년차), 김채연, 박민영, 이지수(2년차)</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>김소윤, 신민석, 김채연, 박민영, 이지수</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>26.07.01~</t>
         </is>
       </c>
-      <c r="E3" s="31" t="inlineStr">
+      <c r="E3" s="25" t="inlineStr">
         <is>
           <t>9월 학술집담회 : 튜머보드, 저널리뷰(김소윤, 신민석, 김채연, 박민영, 이지수)
 9월 면담 : 수련 및 진로 상담(김소윤, 신민석)
@@ -1050,28 +1039,28 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="57" customHeight="1" s="21">
-      <c r="A4" s="11" t="inlineStr">
+    <row r="4" ht="57" customHeight="1" s="9">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>교육전담</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>호정규</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>김소윤, 신민석(1년차), 김채연, 박민영, 이지수(2년차)</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>김소윤, 신민석, 김채연, 박민영, 이지수</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>26.07.01~</t>
         </is>
       </c>
-      <c r="E4" s="31" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>7월 수련지도 : 산과 외래 참관 교육(김채연, 박민영, 이지수)
 8월 수련지도 : 산과 외래 참관 교육(김채연, 박민영, 이지수)
@@ -1079,17 +1068,98 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="21"/>
-    <row r="6" ht="18" customHeight="1" s="21"/>
-    <row r="7" ht="19.5" customHeight="1" s="21"/>
-    <row r="8" ht="19.5" customHeight="1" s="21"/>
-    <row r="9" ht="19.5" customHeight="1" s="21"/>
-    <row r="10" ht="19.5" customHeight="1" s="21"/>
-    <row r="11" ht="19.5" customHeight="1" s="21"/>
-    <row r="12" ht="19.5" customHeight="1" s="21"/>
-    <row r="13" ht="19.5" customHeight="1" s="21"/>
-    <row r="14" ht="19.5" customHeight="1" s="21"/>
+    <row r="5" ht="18" customHeight="1" s="9"/>
+    <row r="6" ht="18" customHeight="1" s="9">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>예시</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1" s="9">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>교육전담</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>한상윤</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>박승민</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>26.07.01~</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>7월 면담 : 인턴 생활 고충·개선사항 상담(이원우, 박승민)
+8월 간담회 : 말초성· 중추성어지럼증감별 (이예닮,정현도)
+8월 면담 : 인턴생활 고충·개선사항 상담 (정현도, 이예닮)
+8월 수련지도 : 외래 업무지도(정현도, 이예닮)
+9월 간담회 (간담회 참여인턴)
+9월 면담 : 인턴생활 고충·개선사항 상담(민현지, 김현진)
+9월 수련지도 : 외래·병동진료 및 수술 준비교육 (김현진, 민현지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19.5" customHeight="1" s="9">
+      <c r="A8" s="27" t="n"/>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1" s="9">
+      <c r="A9" s="27" t="n"/>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+    </row>
+    <row r="10" ht="19.5" customHeight="1" s="9">
+      <c r="A10" s="27" t="n"/>
+      <c r="B10" s="22" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="19.5" customHeight="1" s="9">
+      <c r="A11" s="27" t="n"/>
+      <c r="B11" s="22" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+    </row>
+    <row r="12" ht="19.5" customHeight="1" s="9">
+      <c r="A12" s="27" t="n"/>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+    </row>
+    <row r="13" ht="19.5" customHeight="1" s="9">
+      <c r="A13" s="27" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1" s="9"/>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C7:C13"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="E7:E13"/>
+    <mergeCell ref="D7:D13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>